--- a/ZonasEscolares/excels/JUNIN-CHUPACA-CHUPACA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-CHUPACA-CHUPACA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/JUNIN-CHUPACA-CHUPACA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-CHUPACA-CHUPACA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>303</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.06046</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-75.28948</v>
-      </c>
-      <c r="I2" t="n">
-        <v>220</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.06046</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-75.28948</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>619</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.06517</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-75.27776299999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>41</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.06517</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-75.277763</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>30001-3 19 DE ABRIL</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.0648</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-75.2775</v>
-      </c>
-      <c r="I4" t="n">
-        <v>213</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.0648</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-75.2775</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>30067 / 30067 MANUEL MARIA FLORES</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.063571</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-75.292199</v>
-      </c>
-      <c r="I5" t="n">
-        <v>643</v>
-      </c>
-      <c r="J5" t="n">
-        <v>28</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.063571</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-75.292199</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>30068 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.06049</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-75.29138</v>
-      </c>
-      <c r="I6" t="n">
-        <v>458</v>
-      </c>
-      <c r="J6" t="n">
-        <v>27</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.06049</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-75.29138</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>30072</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.06904</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-75.28742</v>
-      </c>
-      <c r="I7" t="n">
-        <v>214</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.06904</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-75.28742</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>31425 JORGE BASADRE</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.06329</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-75.28422999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>636</v>
-      </c>
-      <c r="J8" t="n">
-        <v>29</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.06329</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-75.28423</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>19 DE ABRIL</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.06564</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-75.27773000000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>891</v>
-      </c>
-      <c r="J9" t="n">
-        <v>42</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.06564</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-75.27773</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>31425 JORGE BASADRE</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.06371</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-75.28417</v>
-      </c>
-      <c r="I10" t="n">
-        <v>631</v>
-      </c>
-      <c r="J10" t="n">
-        <v>33</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.06371</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-75.28417</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>SAN MIGUEL</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.05228</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-75.30083</v>
-      </c>
-      <c r="I11" t="n">
-        <v>221</v>
-      </c>
-      <c r="J11" t="n">
-        <v>19</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.05228</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-75.30083</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>HEROES DE CHUPACA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.08102</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-75.28757</v>
-      </c>
-      <c r="I12" t="n">
-        <v>212</v>
-      </c>
-      <c r="J12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.08102</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-75.28757</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>MAX PLANCK</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.06425</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-75.28497</v>
-      </c>
-      <c r="I13" t="n">
-        <v>281</v>
-      </c>
-      <c r="J13" t="n">
-        <v>14</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.06425</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-75.28497</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>30063</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.0844</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-75.31999999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>221</v>
-      </c>
-      <c r="J14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.0844</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-75.32</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>30064</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.082587</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-75.31165799999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>249</v>
-      </c>
-      <c r="J15" t="n">
-        <v>18</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.082587</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-75.311658</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>AMAUTA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.0783</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-75.3137</v>
-      </c>
-      <c r="I16" t="n">
-        <v>391</v>
-      </c>
-      <c r="J16" t="n">
-        <v>43</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.0783</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-75.3137</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>SANTIAGO LEON</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.130265</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-75.267117</v>
-      </c>
-      <c r="I17" t="n">
-        <v>256</v>
-      </c>
-      <c r="J17" t="n">
-        <v>28</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.130265</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-75.267117</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>30074 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.0221</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-75.3446</v>
-      </c>
-      <c r="I18" t="n">
-        <v>209</v>
-      </c>
-      <c r="J18" t="n">
-        <v>11</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.0221</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-75.3446</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>30080 HEROES DE LA BREÑA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.08135</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-75.24258</v>
-      </c>
-      <c r="I19" t="n">
-        <v>267</v>
-      </c>
-      <c r="J19" t="n">
-        <v>24</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.08135</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-75.24258</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>D'UNI</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.0572</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-75.29055</v>
-      </c>
-      <c r="I20" t="n">
-        <v>239</v>
-      </c>
-      <c r="J20" t="n">
-        <v>14</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.0572</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-75.29055</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>SOL Y FE</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.06458</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-75.28721</v>
-      </c>
-      <c r="I21" t="n">
-        <v>266</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.06458</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-75.28721</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.06345</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-75.29239</v>
-      </c>
-      <c r="I22" t="n">
-        <v>417</v>
-      </c>
-      <c r="J22" t="n">
-        <v>23</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.06345</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-75.29239</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>JHONS HOPKINS</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.06417</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-75.28729</v>
-      </c>
-      <c r="I23" t="n">
-        <v>264</v>
-      </c>
-      <c r="J23" t="n">
-        <v>6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.06417</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-75.28729</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>EXCELLENTIA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.06521</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-75.28482</v>
-      </c>
-      <c r="I24" t="n">
-        <v>507</v>
-      </c>
-      <c r="J24" t="n">
-        <v>24</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.06521</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-75.28482</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>SAN JUAN</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.06516</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-75.28247</v>
-      </c>
-      <c r="I25" t="n">
-        <v>239</v>
-      </c>
-      <c r="J25" t="n">
-        <v>16</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.06516</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-75.28247</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>JOHNS HOPKINS</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.06379</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-75.28716</v>
-      </c>
-      <c r="I26" t="n">
-        <v>530</v>
-      </c>
-      <c r="J26" t="n">
-        <v>29</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.06379</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-75.28716</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/JUNIN-CHUPACA-CHUPACA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-CHUPACA-CHUPACA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>248355</t>
+          <t>248464</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>30072</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.06046</t>
+          <t>-12.06904</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.28948</t>
+          <t>-75.28742</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>248398</t>
+          <t>248987</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>30074 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.06517</t>
+          <t>-12.0221</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.277763</t>
+          <t>-75.3446</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>248416</t>
+          <t>248647</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30067 / 30067 MANUEL MARIA FLORES</t>
+          <t>MAX PLANCK</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.063571</t>
+          <t>-12.06425</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.292199</t>
+          <t>-75.28497</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>281</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>248421</t>
+          <t>511548</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30068 VIRGEN DE FATIMA</t>
+          <t>D'UNI</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.06049</t>
+          <t>-12.0572</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.29138</t>
+          <t>-75.29055</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>248464</t>
+          <t>248746</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30072</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.06904</t>
+          <t>-12.0844</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.28742</t>
+          <t>-75.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>248529</t>
+          <t>248572</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31425 JORGE BASADRE</t>
+          <t>HEROES DE CHUPACA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.06329</t>
+          <t>-12.08102</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.28423</t>
+          <t>-75.28757</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>248548</t>
+          <t>733691</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19 DE ABRIL</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.06564</t>
+          <t>-12.06516</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.27773</t>
+          <t>-75.28247</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>248553</t>
+          <t>248751</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31425 JORGE BASADRE</t>
+          <t>30064</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.06371</t>
+          <t>-12.082587</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.28417</t>
+          <t>-75.311658</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>248572</t>
+          <t>248398</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HEROES DE CHUPACA</t>
+          <t>619</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.08102</t>
+          <t>-12.06517</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.28757</t>
+          <t>-75.277763</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>248647</t>
+          <t>617620</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MAX PLANCK</t>
+          <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.06425</t>
+          <t>-12.06345</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.28497</t>
+          <t>-75.29239</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>417</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>248746</t>
+          <t>249109</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>30080 HEROES DE LA BREÑA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.0844</t>
+          <t>-12.08135</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.32</t>
+          <t>-75.24258</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>248751</t>
+          <t>682941</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>30064</t>
+          <t>EXCELLENTIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.082587</t>
+          <t>-12.06521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.311658</t>
+          <t>-75.28482</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>507</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>248850</t>
+          <t>248421</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AMAUTA</t>
+          <t>30068 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.0783</t>
+          <t>-12.06049</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.3137</t>
+          <t>-75.29138</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>458</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>248930</t>
+          <t>248416</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANTIAGO LEON</t>
+          <t>30067 / 30067 MANUEL MARIA FLORES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.130265</t>
+          <t>-12.063571</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.267117</t>
+          <t>-75.292199</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>643</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>248987</t>
+          <t>248930</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30074 SEÑOR DE LOS MILAGROS</t>
+          <t>SANTIAGO LEON</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.0221</t>
+          <t>-12.130265</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.3446</t>
+          <t>-75.267117</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>256</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>249109</t>
+          <t>248529</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30080 HEROES DE LA BREÑA</t>
+          <t>31425 JORGE BASADRE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.08135</t>
+          <t>-12.06329</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.24258</t>
+          <t>-75.28423</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>636</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>511548</t>
+          <t>825836</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D'UNI</t>
+          <t>JOHNS HOPKINS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.0572</t>
+          <t>-12.06379</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.29055</t>
+          <t>-75.28716</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>530</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>564966</t>
+          <t>248553</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SOL Y FE</t>
+          <t>31425 JORGE BASADRE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.06458</t>
+          <t>-12.06371</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.28721</t>
+          <t>-75.28417</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>631</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>617620</t>
+          <t>564966</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS</t>
+          <t>SOL Y FE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.06345</t>
+          <t>-12.06458</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.29239</t>
+          <t>-75.28721</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>644176</t>
+          <t>248548</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JHONS HOPKINS</t>
+          <t>19 DE ABRIL</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.06417</t>
+          <t>-12.06564</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.28729</t>
+          <t>-75.27773</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>891</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>682941</t>
+          <t>248850</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EXCELLENTIA</t>
+          <t>AMAUTA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.06521</t>
+          <t>-12.0783</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.28482</t>
+          <t>-75.3137</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>391</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>733691</t>
+          <t>644176</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>JHONS HOPKINS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.06516</t>
+          <t>-12.06417</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.28247</t>
+          <t>-75.28729</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>825836</t>
+          <t>248355</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JOHNS HOPKINS</t>
+          <t>303</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.06379</t>
+          <t>-12.06046</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.28716</t>
+          <t>-75.28948</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-CHUPACA-CHUPACA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-CHUPACA-CHUPACA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>248464</t>
+          <t>825836</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30072</t>
+          <t>JOHNS HOPKINS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.06904</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.28742</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-12.06379</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-75.28716</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>248987</t>
+          <t>733691</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30074 SEÑOR DE LOS MILAGROS</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.0221</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.3446</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-12.06516</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-75.28247</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>248402</t>
+          <t>682941</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30001-3 19 DE ABRIL</t>
+          <t>EXCELLENTIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.0648</t>
+          <t>507</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.2775</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-12.06521</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-75.28482</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>248647</t>
+          <t>644176</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MAX PLANCK</t>
+          <t>JHONS HOPKINS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.06425</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.28497</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>-12.06417</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.28729</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>511548</t>
+          <t>617620</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D'UNI</t>
+          <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.0572</t>
+          <t>417</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.29055</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-12.06345</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.29239</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>248746</t>
+          <t>564966</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>SOL Y FE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.0844</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.32</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-12.06458</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.28721</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>248572</t>
+          <t>511548</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HEROES DE CHUPACA</t>
+          <t>D'UNI</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.08102</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.28757</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-12.0572</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-75.29055</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>733691</t>
+          <t>249109</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>30080 HEROES DE LA BREÑA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.06516</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.28247</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-12.08135</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-75.24258</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>248751</t>
+          <t>248987</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30064</t>
+          <t>30074 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.082587</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.311658</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-12.0221</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-75.3446</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>248567</t>
+          <t>248930</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>SANTIAGO LEON</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.05228</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.30083</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-12.130265</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.267117</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>248398</t>
+          <t>248850</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>AMAUTA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.06517</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.277763</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-12.0783</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-75.3137</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>617620</t>
+          <t>248751</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS</t>
+          <t>30064</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.06345</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.29239</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>-12.082587</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.311658</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>249109</t>
+          <t>248746</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30080 HEROES DE LA BREÑA</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.08135</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.24258</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-12.0844</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-75.32</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>682941</t>
+          <t>248647</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>EXCELLENTIA</t>
+          <t>MAX PLANCK</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.06521</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.28482</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>-12.06425</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-75.28497</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>248421</t>
+          <t>248572</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30068 VIRGEN DE FATIMA</t>
+          <t>HEROES DE CHUPACA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.06049</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.29138</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>-12.08102</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-75.28757</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>248416</t>
+          <t>248567</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>30067 / 30067 MANUEL MARIA FLORES</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.063571</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.292199</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>-12.05228</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-75.30083</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>248930</t>
+          <t>248553</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANTIAGO LEON</t>
+          <t>31425 JORGE BASADRE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.130265</t>
+          <t>631</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.267117</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>-12.06371</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-75.28417</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>248529</t>
+          <t>248548</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>31425 JORGE BASADRE</t>
+          <t>19 DE ABRIL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.06329</t>
+          <t>891</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.28423</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>-12.06564</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-75.27773</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>825836</t>
+          <t>248529</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JOHNS HOPKINS</t>
+          <t>31425 JORGE BASADRE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.06379</t>
+          <t>636</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.28716</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>-12.06329</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-75.28423</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>248553</t>
+          <t>248464</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31425 JORGE BASADRE</t>
+          <t>30072</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.06371</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.28417</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>-12.06904</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-75.28742</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>564966</t>
+          <t>248421</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SOL Y FE</t>
+          <t>30068 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.06458</t>
+          <t>458</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.28721</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-12.06049</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-75.29138</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>248548</t>
+          <t>248416</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>19 DE ABRIL</t>
+          <t>30067 / 30067 MANUEL MARIA FLORES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.06564</t>
+          <t>643</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.27773</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>-12.063571</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-75.292199</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>248850</t>
+          <t>248402</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AMAUTA</t>
+          <t>30001-3 19 DE ABRIL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.0783</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.3137</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>-12.0648</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-75.2775</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>644176</t>
+          <t>248398</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JHONS HOPKINS</t>
+          <t>619</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.06417</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.28729</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-12.06517</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-75.277763</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1999,22 +1999,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>-12.06046</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>-75.28948</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-CHUPACA-CHUPACA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-CHUPACA-CHUPACA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
